--- a/30_Tieu_De_BNI_Topaz_Chapter_Online.xlsx
+++ b/30_Tieu_De_BNI_Topaz_Chapter_Online.xlsx
@@ -460,7 +460,7 @@
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="35" customWidth="1" min="9" max="9"/>
